--- a/reports/visit_details/visit_details_moses-thulare-moshwane.xlsx
+++ b/reports/visit_details/visit_details_moses-thulare-moshwane.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D124"/>
+  <dimension ref="A1:D125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3156,6 +3156,28 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>8507041104080</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Thobile Maziya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/visit_details/visit_details_moses-thulare-moshwane.xlsx
+++ b/reports/visit_details/visit_details_moses-thulare-moshwane.xlsx
@@ -419,11 +419,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D125"/>
+  <dimension ref="A1:D187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
@@ -3178,6 +3178,1370 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>7895295780089</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Monde Modikwe</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>8411251232089</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Toilet Baloyi</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>7603215560081</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Speelman Masango</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>7608281153083</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Letty Sithole</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>6905080329083</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Annacleha Moloi</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>7810090324083</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Elisa Dibitso</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>8808290518081</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Tsakane Ngobeni</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>7505040862089</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Constance Rebombo</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>7901235883081</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Lucas Lehlaka</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>9606135738081</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Sibusiso Nkosi</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>0306015474082</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Alfred Ramokgopo</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>7402030368089</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Merriam Bambo</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>7209061068086</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Anna Nkosi</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>7004225333082</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Joseph Harry Manganye</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>7901017805081</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Khutso Maeko</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>9905015429088</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Lifa Masina</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>7609291067081</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Maria Poppy Mathonsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>9507056019081</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Koketso Mahlangu</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>7703076346081</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Seleka Motau</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>0008246302080</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Andile Ndlangamandla</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>6605150472082</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Maria Matlou</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>5501280735082</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Maria Matlou</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>6109100680084</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Rosina Masela</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>9709161291080</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Nthabiseng Lefoka</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>9311115975080</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Afios Mthimunye</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>8409021255083</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Caroline Molefe</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>9106305906089</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Hendrick Masuku</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>AB1524692</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Kenneth Ndzovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>9904166397087</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Tebogo Mnisi</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>9104115546088</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Kagiso Tobotsane</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>0403216162087</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Molebogeng Tobotsane</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>0201210347088</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Keletso Ramabina</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>8005050913087</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Nhlamulo Banyini</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>9702171426085</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Itumeleng Seabi</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>9903060510084</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Tshepiso Mabusela</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>AE420380</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Samantha Nkomo</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>8806206469084</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Ntando Nhlangulela</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>0312265498088</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Kamogelo Kau</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>9404295383082</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Oageng Padi</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>9405250590082</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Sarah Modibela</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>9701265331086</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Mosa Maluleke</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>8812225398080</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Sello Cry Matsiba</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>9206296132081</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Maphuti Mokowelele</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>9004146158087</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Frans Dolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>8009024455084</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Stanley Motlokwane</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>8908296228089</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Tshepo Mohale</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>8404260968082</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Nkele Elizabeth Kgopa</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>9404261355080</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Deliwe Ntwanambi</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>8507251440083</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Mpho Makhubela</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>FN643727</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Praisemore Mpofu</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>FN607588</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Praymore Magomo</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Ae274842</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Nqobile Ndhlovu</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>AB2027097</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Estevao Moyane</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>9406085762086</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Thulani Shabalala</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>7301060733081</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Bridgert Chauke</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>850914553084</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Solly Ditlhake</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>0404265448088</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Xolani Mtsweni</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>9411260882089</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Tumi Kgwale</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>9628086010088</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Kgomotso Majadibodu</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>9209206014084</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Mpho Moselane</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>9811100909085</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Liza Setati</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Moses Thulare Moshwane</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>11-Oct</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>8901261054085</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Ngaletsane Jane Maake</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
